--- a/tests/testdata/excel/ファイル名/🍣メニュー.xlsx
+++ b/tests/testdata/excel/ファイル名/🍣メニュー.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF3E988B-8525-484C-BCDB-78E42035635E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A9BC9D2-EC54-4961-A06B-0A2889E65E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{C006750D-AF6E-458B-87C5-99554C9C4387}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{99EB61AF-C7AD-485E-BB52-EDCC3E0615A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{974794C1-9EA6-47FA-A061-C7B2E7358A92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE939C2-B98A-4E75-8D64-8F26B71D53DA}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/🍣メニュー.xlsx
+++ b/tests/testdata/excel/ファイル名/🍣メニュー.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A9BC9D2-EC54-4961-A06B-0A2889E65E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{008C466C-0294-455B-ABC9-91ED60E98A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{99EB61AF-C7AD-485E-BB52-EDCC3E0615A5}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{FB7DB0DD-89DC-4499-B63F-CFEE47D2F444}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE939C2-B98A-4E75-8D64-8F26B71D53DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141203C9-421B-4BDC-85A0-B02424C2A9EF}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
